--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260915.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260915.xlsx
@@ -601,17 +601,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>10,700,000</t>
+          <t>6,378,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -623,22 +623,22 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>6,323,000</t>
+          <t>10,931,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
@@ -667,88 +667,88 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>22,333,000</t>
+          <t>37,056,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,331,000</t>
+          <t>22,333,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>37,056,000</t>
+          <t>50,995,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>50,095,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -770,29 +770,29 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,043,682,396</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -814,95 +814,95 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,845,000</t>
+          <t>27,131,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>27,131,000</t>
+          <t>35,990,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>35,990,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>6,897,000</t>
+          <t>3,756,195,604</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -968,46 +968,46 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>9,933,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>9,933,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,270,000</t>
+          <t>2,322,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,594,000</t>
+          <t>9,893,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,248,000</t>
+          <t>18,807,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1195,127 +1195,127 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>5,434,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,324,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>2,562,601,204</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,581,961,204</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>17,775,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>17,277,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,795,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1371,66 +1371,66 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>14,913,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>14,913,000</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>52,799,000</t>
+          <t>54,146,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1672,29 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>16,823,000</t>
+          <t>19,286,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,491,000</t>
+          <t>16,823,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-128,648,250</t>
+          <t>-60,583,107</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
     </row>
